--- a/outputs/aasted3_run_comparison/runs/17_3_f_m_aa3_25_06_26_2160_4374s/reports/aasted3_reference_based_comparison_summary.xlsx
+++ b/outputs/aasted3_run_comparison/runs/17_3_f_m_aa3_25_06_26_2160_4374s/reports/aasted3_reference_based_comparison_summary.xlsx
@@ -13064,7 +13064,7 @@
         <v>2.5</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8018543671750219</v>
+        <v>-0.8066211997382844</v>
       </c>
       <c r="N4" t="n">
         <v>1.23716366640188</v>
